--- a/Design/Excel/ET/Datas/Product/DishStageConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/DishStageConfig.xlsx
@@ -1128,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1697,6 +1697,228 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>14,15</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>16,17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Design/Excel/ET/Datas/Product/DishStageConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/DishStageConfig.xlsx
@@ -1,669 +1,730 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UnitProto" sheetId="1" r:id="R2b1dda55715c4d8f"/>
-  </x:sheets>
-</x:workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UnitProto" sheetId="1" state="visible" r:id="rId1"/>
+  </sheets>
+  <definedNames/>
+</workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
-    <x:numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <x:numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <x:numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <x:numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </x:numFmts>
-  <x:fonts count="24">
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="9"/>
-      <x:color theme="1"/>
-      <x:name val="微软雅黑"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="微软雅黑"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="9"/>
-      <x:color theme="1"/>
-      <x:name val="微软雅黑"/>
-    </x:font>
-    <x:font>
-      <x:sz val="12"/>
-      <x:color theme="1"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:u val="single"/>
-      <x:sz val="11"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:u val="single"/>
-      <x:sz val="11"/>
-      <x:color rgb="FF800080"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FFFF0000"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="18"/>
-      <x:color theme="3"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:i/>
-      <x:sz val="11"/>
-      <x:color rgb="FF7F7F7F"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="15"/>
-      <x:color theme="3"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="13"/>
-      <x:color theme="3"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color theme="3"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF3F3F76"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FF3F3F3F"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFFA7D00"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FFFA7D00"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF006100"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF9C0006"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF9C6500"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="0"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="34">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF92D050"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFFCC"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFCC99"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF2F2F2"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFA5A5A5"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFC6EFCE"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFC7CE"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFEB9C"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="4"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="4" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="4" tint="0.59999"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="4" tint="0.39998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="5"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="5" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="5" tint="0.59999"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="5" tint="0.39998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="6"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="6" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="6" tint="0.59999"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="6" tint="0.39998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="7"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="7" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="7" tint="0.59999"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="7" tint="0.39998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="8"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="8" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="8" tint="0.59999"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="8" tint="0.39998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="9"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="9" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="9" tint="0.59999"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="9" tint="0.39998"/>
-      </x:patternFill>
-    </x:fill>
-  </x:fills>
-  <x:borders count="9">
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFB2B2B2"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFB2B2B2"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFB2B2B2"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFB2B2B2"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom style="medium">
-        <x:color theme="4"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom style="medium">
-        <x:color theme="4" tint="0.49998"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF3F3F3F"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FF3F3F3F"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF3F3F3F"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF3F3F3F"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="double">
-        <x:color rgb="FF3F3F3F"/>
-      </x:left>
-      <x:right style="double">
-        <x:color rgb="FF3F3F3F"/>
-      </x:right>
-      <x:top style="double">
-        <x:color rgb="FF3F3F3F"/>
-      </x:top>
-      <x:bottom style="double">
-        <x:color rgb="FF3F3F3F"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom style="double">
-        <x:color rgb="FFFF8001"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top style="thin">
-        <x:color theme="4"/>
-      </x:top>
-      <x:bottom style="double">
-        <x:color theme="4"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-  </x:borders>
-  <x:cellStyleXfs count="50">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <x:xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </x:cellStyleXfs>
-  <x:cellXfs count="6">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-  </x:cellXfs>
-  <x:cellStyles count="50">
-    <x:cellStyle name="常规" xfId="0"/>
-    <x:cellStyle name="千位分隔" xfId="1"/>
-    <x:cellStyle name="货币" xfId="2"/>
-    <x:cellStyle name="百分比" xfId="3"/>
-    <x:cellStyle name="千位分隔[0]" xfId="4"/>
-    <x:cellStyle name="货币[0]" xfId="5"/>
-    <x:cellStyle name="超链接" xfId="6"/>
-    <x:cellStyle name="已访问的超链接" xfId="7"/>
-    <x:cellStyle name="注释" xfId="8"/>
-    <x:cellStyle name="警告文本" xfId="9"/>
-    <x:cellStyle name="标题" xfId="10"/>
-    <x:cellStyle name="解释性文本" xfId="11"/>
-    <x:cellStyle name="标题 1" xfId="12"/>
-    <x:cellStyle name="标题 2" xfId="13"/>
-    <x:cellStyle name="标题 3" xfId="14"/>
-    <x:cellStyle name="标题 4" xfId="15"/>
-    <x:cellStyle name="输入" xfId="16"/>
-    <x:cellStyle name="输出" xfId="17"/>
-    <x:cellStyle name="计算" xfId="18"/>
-    <x:cellStyle name="检查单元格" xfId="19"/>
-    <x:cellStyle name="链接单元格" xfId="20"/>
-    <x:cellStyle name="汇总" xfId="21"/>
-    <x:cellStyle name="好" xfId="22"/>
-    <x:cellStyle name="差" xfId="23"/>
-    <x:cellStyle name="适中" xfId="24"/>
-    <x:cellStyle name="强调文字颜色 1" xfId="25"/>
-    <x:cellStyle name="20% - 强调文字颜色 1" xfId="26"/>
-    <x:cellStyle name="40% - 强调文字颜色 1" xfId="27"/>
-    <x:cellStyle name="60% - 强调文字颜色 1" xfId="28"/>
-    <x:cellStyle name="强调文字颜色 2" xfId="29"/>
-    <x:cellStyle name="20% - 强调文字颜色 2" xfId="30"/>
-    <x:cellStyle name="40% - 强调文字颜色 2" xfId="31"/>
-    <x:cellStyle name="60% - 强调文字颜色 2" xfId="32"/>
-    <x:cellStyle name="强调文字颜色 3" xfId="33"/>
-    <x:cellStyle name="20% - 强调文字颜色 3" xfId="34"/>
-    <x:cellStyle name="40% - 强调文字颜色 3" xfId="35"/>
-    <x:cellStyle name="60% - 强调文字颜色 3" xfId="36"/>
-    <x:cellStyle name="强调文字颜色 4" xfId="37"/>
-    <x:cellStyle name="20% - 强调文字颜色 4" xfId="38"/>
-    <x:cellStyle name="40% - 强调文字颜色 4" xfId="39"/>
-    <x:cellStyle name="60% - 强调文字颜色 4" xfId="40"/>
-    <x:cellStyle name="强调文字颜色 5" xfId="41"/>
-    <x:cellStyle name="20% - 强调文字颜色 5" xfId="42"/>
-    <x:cellStyle name="40% - 强调文字颜色 5" xfId="43"/>
-    <x:cellStyle name="60% - 强调文字颜色 5" xfId="44"/>
-    <x:cellStyle name="强调文字颜色 6" xfId="45"/>
-    <x:cellStyle name="20% - 强调文字颜色 6" xfId="46"/>
-    <x:cellStyle name="40% - 强调文字颜色 6" xfId="47"/>
-    <x:cellStyle name="60% - 强调文字颜色 6" xfId="48"/>
-    <x:cellStyle name="常规 2" xfId="49"/>
-  </x:cellStyles>
-</x:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="24">
+    <font>
+      <name val="宋体"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color theme="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="34">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="9">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.49998"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="50">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="50">
+    <cellStyle name="常规" xfId="0"/>
+    <cellStyle name="千位分隔" xfId="1"/>
+    <cellStyle name="货币" xfId="2"/>
+    <cellStyle name="百分比" xfId="3"/>
+    <cellStyle name="千位分隔[0]" xfId="4"/>
+    <cellStyle name="货币[0]" xfId="5"/>
+    <cellStyle name="超链接" xfId="6"/>
+    <cellStyle name="已访问的超链接" xfId="7"/>
+    <cellStyle name="注释" xfId="8"/>
+    <cellStyle name="警告文本" xfId="9"/>
+    <cellStyle name="标题" xfId="10"/>
+    <cellStyle name="解释性文本" xfId="11"/>
+    <cellStyle name="标题 1" xfId="12"/>
+    <cellStyle name="标题 2" xfId="13"/>
+    <cellStyle name="标题 3" xfId="14"/>
+    <cellStyle name="标题 4" xfId="15"/>
+    <cellStyle name="输入" xfId="16"/>
+    <cellStyle name="输出" xfId="17"/>
+    <cellStyle name="计算" xfId="18"/>
+    <cellStyle name="检查单元格" xfId="19"/>
+    <cellStyle name="链接单元格" xfId="20"/>
+    <cellStyle name="汇总" xfId="21"/>
+    <cellStyle name="好" xfId="22"/>
+    <cellStyle name="差" xfId="23"/>
+    <cellStyle name="适中" xfId="24"/>
+    <cellStyle name="强调文字颜色 1" xfId="25"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28"/>
+    <cellStyle name="强调文字颜色 2" xfId="29"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32"/>
+    <cellStyle name="强调文字颜色 3" xfId="33"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36"/>
+    <cellStyle name="强调文字颜色 4" xfId="37"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40"/>
+    <cellStyle name="强调文字颜色 5" xfId="41"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44"/>
+    <cellStyle name="强调文字颜色 6" xfId="45"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48"/>
+    <cellStyle name="常规 2" xfId="49"/>
+  </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -940,65 +1001,70 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G89"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
-    <col min="3" max="4" width="12.625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="28.75" style="2" customWidth="1"/>
-    <col min="8" max="9" width="11.75" style="2" customWidth="1"/>
-    <col min="10" max="10" width="6.75" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2" customWidth="0"/>
+    <col width="21.125" customWidth="1" style="2" min="1" max="1"/>
+    <col width="12.75" customWidth="1" style="2" min="2" max="2"/>
+    <col width="12.625" customWidth="1" style="2" min="3" max="4"/>
+    <col width="15.125" customWidth="1" style="2" min="5" max="5"/>
+    <col width="9.625" customWidth="1" style="2" min="6" max="6"/>
+    <col width="28.75" customWidth="1" style="2" min="7" max="7"/>
+    <col width="11.75" customWidth="1" style="2" min="8" max="9"/>
+    <col width="6.75" customWidth="1" style="2" min="10" max="10"/>
+    <col width="9" customWidth="1" style="2" min="11" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">##var</t>
+          <t>##var</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Id</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kind</t>
+          <t>Kind</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">RecipeId</t>
+          <t>RecipeId</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">OutputDefinitionId</t>
+          <t>OutputDefinitionId</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ContainerDefinitionId</t>
+          <t>ContainerDefinitionId</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">DependencyIds</t>
+          <t>DependencyIds</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">##type</t>
+          <t>##type</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1008,71 +1074,66 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(list#sep=,),int</t>
+          <t>(list#sep=,),int</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">##</t>
+          <t>##</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Id</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kind</t>
+          <t>Kind</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">RecipeId</t>
+          <t>RecipeId</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">OutputDefinitionId</t>
+          <t>OutputDefinitionId</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ContainerDefinitionId</t>
+          <t>ContainerDefinitionId</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DependencyIds</t>
+          <t>DependencyIds</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1082,34 +1143,24 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1119,34 +1170,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1156,34 +1202,24 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1193,34 +1229,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3,5</t>
+          <t>3,5</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1230,34 +1261,24 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1267,34 +1288,24 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1304,34 +1315,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2,4,6</t>
+          <t>2,4,6</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1341,34 +1347,29 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7,5</t>
+          <t>7,5</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1378,34 +1379,24 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1415,34 +1406,29 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1452,34 +1438,24 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1489,34 +1465,29 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">10,11</t>
+          <t>10,11</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1526,34 +1497,24 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1563,34 +1524,29 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1600,34 +1556,24 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1637,34 +1583,29 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">14,15</t>
+          <t>14,15</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1674,34 +1615,24 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,27 +1642,26 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">16,17</t>
+          <t>16,17</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="str"/>
       <c r="B22" t="n">
         <v>19</v>
       </c>
@@ -1749,10 +1679,8 @@
       <c r="F22" t="n">
         <v>0</v>
       </c>
-      <c r="G22" t="str"/>
     </row>
     <row r="23">
-      <c r="A23" t="str"/>
       <c r="B23" t="n">
         <v>20</v>
       </c>
@@ -1770,12 +1698,13 @@
       <c r="F23" t="n">
         <v>0</v>
       </c>
-      <c r="G23" t="str">
-        <v>19</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="str"/>
       <c r="B24" t="n">
         <v>21</v>
       </c>
@@ -1793,10 +1722,8 @@
       <c r="F24" t="n">
         <v>0</v>
       </c>
-      <c r="G24" t="str"/>
     </row>
     <row r="25">
-      <c r="A25" t="str"/>
       <c r="B25" t="n">
         <v>22</v>
       </c>
@@ -1814,12 +1741,13 @@
       <c r="F25" t="n">
         <v>0</v>
       </c>
-      <c r="G25" t="str">
-        <v>21</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str"/>
       <c r="B26" t="n">
         <v>23</v>
       </c>
@@ -1837,10 +1765,8 @@
       <c r="F26" t="n">
         <v>0</v>
       </c>
-      <c r="G26" t="str"/>
     </row>
     <row r="27">
-      <c r="A27" t="str"/>
       <c r="B27" t="n">
         <v>24</v>
       </c>
@@ -1858,12 +1784,13 @@
       <c r="F27" t="n">
         <v>10</v>
       </c>
-      <c r="G27" t="str">
-        <v>2,20,22,11</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2,20,22,11</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str"/>
       <c r="B28" t="n">
         <v>25</v>
       </c>
@@ -1881,12 +1808,13 @@
       <c r="F28" t="n">
         <v>10</v>
       </c>
-      <c r="G28" t="str">
-        <v>2,20,22,23,11</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2,20,22,23,11</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="str"/>
       <c r="B29" t="n">
         <v>26</v>
       </c>
@@ -1904,10 +1832,8 @@
       <c r="F29" t="n">
         <v>0</v>
       </c>
-      <c r="G29" t="str"/>
     </row>
     <row r="30">
-      <c r="A30" t="str"/>
       <c r="B30" t="n">
         <v>27</v>
       </c>
@@ -1925,10 +1851,8 @@
       <c r="F30" t="n">
         <v>0</v>
       </c>
-      <c r="G30" t="str"/>
     </row>
     <row r="31">
-      <c r="A31" t="str"/>
       <c r="B31" t="n">
         <v>28</v>
       </c>
@@ -1946,10 +1870,8 @@
       <c r="F31" t="n">
         <v>0</v>
       </c>
-      <c r="G31" t="str"/>
     </row>
     <row r="32">
-      <c r="A32" t="str"/>
       <c r="B32" t="n">
         <v>29</v>
       </c>
@@ -1967,12 +1889,13 @@
       <c r="F32" t="n">
         <v>10</v>
       </c>
-      <c r="G32" t="str">
-        <v>27,30,11</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>27,30,11</t>
+        </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="str"/>
       <c r="B33" t="n">
         <v>30</v>
       </c>
@@ -1990,12 +1913,13 @@
       <c r="F33" t="n">
         <v>0</v>
       </c>
-      <c r="G33" t="str">
-        <v>28</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str"/>
       <c r="B34" t="n">
         <v>31</v>
       </c>
@@ -2013,10 +1937,8 @@
       <c r="F34" t="n">
         <v>0</v>
       </c>
-      <c r="G34" t="str"/>
     </row>
     <row r="35">
-      <c r="A35" t="str"/>
       <c r="B35" t="n">
         <v>32</v>
       </c>
@@ -2034,12 +1956,13 @@
       <c r="F35" t="n">
         <v>0</v>
       </c>
-      <c r="G35" t="str">
-        <v>31</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str"/>
       <c r="B36" t="n">
         <v>33</v>
       </c>
@@ -2057,12 +1980,13 @@
       <c r="F36" t="n">
         <v>10</v>
       </c>
-      <c r="G36" t="str">
-        <v>32,34,10,11</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>32,34,10,11</t>
+        </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str"/>
       <c r="B37" t="n">
         <v>34</v>
       </c>
@@ -2080,12 +2004,13 @@
       <c r="F37" t="n">
         <v>0</v>
       </c>
-      <c r="G37" t="str">
-        <v>3</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str"/>
       <c r="B38" t="n">
         <v>35</v>
       </c>
@@ -2103,10 +2028,8 @@
       <c r="F38" t="n">
         <v>0</v>
       </c>
-      <c r="G38" t="str"/>
     </row>
     <row r="39">
-      <c r="A39" t="str"/>
       <c r="B39" t="n">
         <v>36</v>
       </c>
@@ -2124,10 +2047,8 @@
       <c r="F39" t="n">
         <v>0</v>
       </c>
-      <c r="G39" t="str"/>
     </row>
     <row r="40">
-      <c r="A40" t="str"/>
       <c r="B40" t="n">
         <v>37</v>
       </c>
@@ -2145,10 +2066,8 @@
       <c r="F40" t="n">
         <v>0</v>
       </c>
-      <c r="G40" t="str"/>
     </row>
     <row r="41">
-      <c r="A41" t="str"/>
       <c r="B41" t="n">
         <v>38</v>
       </c>
@@ -2166,12 +2085,13 @@
       <c r="F41" t="n">
         <v>45</v>
       </c>
-      <c r="G41" t="str">
-        <v>35,3,36,37</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>35,3,36,37</t>
+        </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="str"/>
       <c r="B42" t="n">
         <v>39</v>
       </c>
@@ -2189,10 +2109,8 @@
       <c r="F42" t="n">
         <v>0</v>
       </c>
-      <c r="G42" t="str"/>
     </row>
     <row r="43">
-      <c r="A43" t="str"/>
       <c r="B43" t="n">
         <v>40</v>
       </c>
@@ -2210,12 +2128,13 @@
       <c r="F43" t="n">
         <v>47</v>
       </c>
-      <c r="G43" t="str">
-        <v>38,39</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>38,39</t>
+        </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="str"/>
       <c r="B44" t="n">
         <v>41</v>
       </c>
@@ -2233,12 +2152,13 @@
       <c r="F44" t="n">
         <v>47</v>
       </c>
-      <c r="G44" t="str">
-        <v>40</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="str"/>
       <c r="B45" t="n">
         <v>42</v>
       </c>
@@ -2256,10 +2176,8 @@
       <c r="F45" t="n">
         <v>0</v>
       </c>
-      <c r="G45" t="str"/>
     </row>
     <row r="46">
-      <c r="A46" t="str"/>
       <c r="B46" t="n">
         <v>43</v>
       </c>
@@ -2277,12 +2195,13 @@
       <c r="F46" t="n">
         <v>49</v>
       </c>
-      <c r="G46" t="str">
-        <v>41,42</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>41,42</t>
+        </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="str"/>
       <c r="B47" t="n">
         <v>44</v>
       </c>
@@ -2300,10 +2219,8 @@
       <c r="F47" t="n">
         <v>0</v>
       </c>
-      <c r="G47" t="str"/>
     </row>
     <row r="48">
-      <c r="A48" t="str"/>
       <c r="B48" t="n">
         <v>45</v>
       </c>
@@ -2321,12 +2238,13 @@
       <c r="F48" t="n">
         <v>0</v>
       </c>
-      <c r="G48" t="str">
-        <v>44</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="str"/>
       <c r="B49" t="n">
         <v>46</v>
       </c>
@@ -2344,10 +2262,8 @@
       <c r="F49" t="n">
         <v>0</v>
       </c>
-      <c r="G49" t="str"/>
     </row>
     <row r="50">
-      <c r="A50" t="str"/>
       <c r="B50" t="n">
         <v>47</v>
       </c>
@@ -2365,12 +2281,13 @@
       <c r="F50" t="n">
         <v>54</v>
       </c>
-      <c r="G50" t="str">
-        <v>45,46</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>45,46</t>
+        </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="str"/>
       <c r="B51" t="n">
         <v>48</v>
       </c>
@@ -2388,10 +2305,8 @@
       <c r="F51" t="n">
         <v>0</v>
       </c>
-      <c r="G51" t="str"/>
     </row>
     <row r="52">
-      <c r="A52" t="str"/>
       <c r="B52" t="n">
         <v>49</v>
       </c>
@@ -2409,12 +2324,13 @@
       <c r="F52" t="n">
         <v>59</v>
       </c>
-      <c r="G52" t="str">
-        <v>47,48</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>47,48</t>
+        </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="str"/>
       <c r="B53" t="n">
         <v>50</v>
       </c>
@@ -2432,10 +2348,8 @@
       <c r="F53" t="n">
         <v>0</v>
       </c>
-      <c r="G53" t="str"/>
     </row>
     <row r="54">
-      <c r="A54" t="str"/>
       <c r="B54" t="n">
         <v>51</v>
       </c>
@@ -2453,12 +2367,13 @@
       <c r="F54" t="n">
         <v>55</v>
       </c>
-      <c r="G54" t="str">
-        <v>36,50</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>36,50</t>
+        </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="str"/>
       <c r="B55" t="n">
         <v>52</v>
       </c>
@@ -2476,12 +2391,13 @@
       <c r="F55" t="n">
         <v>59</v>
       </c>
-      <c r="G55" t="str">
-        <v>51,48</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>51,48</t>
+        </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="str"/>
       <c r="B56" t="n">
         <v>53</v>
       </c>
@@ -2499,12 +2415,13 @@
       <c r="F56" t="n">
         <v>59</v>
       </c>
-      <c r="G56" t="str">
-        <v>49,52,48</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>49,52,48</t>
+        </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="str"/>
       <c r="B57" t="n">
         <v>54</v>
       </c>
@@ -2522,12 +2439,13 @@
       <c r="F57" t="n">
         <v>55</v>
       </c>
-      <c r="G57" t="str">
-        <v>36,50</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>36,50</t>
+        </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="str"/>
       <c r="B58" t="n">
         <v>55</v>
       </c>
@@ -2545,12 +2463,13 @@
       <c r="F58" t="n">
         <v>59</v>
       </c>
-      <c r="G58" t="str">
-        <v>54,48</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>54,48</t>
+        </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="str"/>
       <c r="B59" t="n">
         <v>56</v>
       </c>
@@ -2568,8 +2487,650 @@
       <c r="F59" t="n">
         <v>59</v>
       </c>
-      <c r="G59" t="str">
-        <v>49,52,55,48</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>49,52,55,48</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>57</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>64</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>58</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>12</v>
+      </c>
+      <c r="E61" t="n">
+        <v>65</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>59</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>66</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>60</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>67</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>61</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>72</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>62</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Assembly</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>13</v>
+      </c>
+      <c r="E65" t="n">
+        <v>68</v>
+      </c>
+      <c r="F65" t="n">
+        <v>72</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>58,59,61</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>63</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Assembly</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>14</v>
+      </c>
+      <c r="E66" t="n">
+        <v>69</v>
+      </c>
+      <c r="F66" t="n">
+        <v>72</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>62,60,61</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>64</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Steam</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>7</v>
+      </c>
+      <c r="E67" t="n">
+        <v>70</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>65</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>71</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>66</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>AddToContainer</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>70</v>
+      </c>
+      <c r="F69" t="n">
+        <v>71</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>64,65</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>67</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>76</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>68</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>77</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>69</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>87</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>70</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>7</v>
+      </c>
+      <c r="E73" t="n">
+        <v>78</v>
+      </c>
+      <c r="F73" t="n">
+        <v>87</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>67,68,69</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>71</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>59</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>72</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Portion</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>78</v>
+      </c>
+      <c r="F75" t="n">
+        <v>59</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>70,71</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>73</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>44</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>74</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>81</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>75</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>85</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>76</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Portion</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>78</v>
+      </c>
+      <c r="F79" t="n">
+        <v>85</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>70,75</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>77</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>8</v>
+      </c>
+      <c r="E80" t="n">
+        <v>82</v>
+      </c>
+      <c r="F80" t="n">
+        <v>85</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>76,73,74,75</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>78</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>84</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>79</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Portion</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>82</v>
+      </c>
+      <c r="F82" t="n">
+        <v>84</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>77,78</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>80</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>83</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>81</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Blend</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>15</v>
+      </c>
+      <c r="E84" t="n">
+        <v>88</v>
+      </c>
+      <c r="F84" t="n">
+        <v>84</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>79,80,78</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>82</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>79</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>83</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>8</v>
+      </c>
+      <c r="E86" t="n">
+        <v>80</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>84</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>86</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>85</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>AddToContainer</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>80</v>
+      </c>
+      <c r="F88" t="n">
+        <v>86</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>83,84</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>86</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Blend</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>16</v>
+      </c>
+      <c r="E89" t="n">
+        <v>89</v>
+      </c>
+      <c r="F89" t="n">
+        <v>84</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>85,79,80,78</t>
+        </is>
       </c>
     </row>
   </sheetData>
